--- a/マンホールカードの情報.xlsx
+++ b/マンホールカードの情報.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hiro7\OneDrive\ドキュメント\アプリ開発\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EC71717-0704-45B8-8703-BE33732D6A09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76FB72D7-F4C8-48DD-A7E4-C0965DE587B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="10170" firstSheet="2" activeTab="2" xr2:uid="{0246ACEA-FE81-4772-91CB-A927D5B338F5}"/>
   </bookViews>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="708" uniqueCount="455">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="708" uniqueCount="456">
   <si>
     <t>こちらからご確認ください</t>
   </si>
@@ -1902,12 +1902,6 @@
 電話：098-886-2020</t>
   </si>
   <si>
-    <t>8:00～19:30（4～6月､10月､11月）　
-8:00～20:30（7～9月）
-8:00～18:30（12～3月）
-（7月の第1水曜日とその翌日は休み）</t>
-  </si>
-  <si>
     <t>那覇市
 (A001)</t>
   </si>
@@ -1920,10 +1914,6 @@
 電話：098-941-7808</t>
   </si>
   <si>
-    <t>9：00～20：00
-ただし1月1日はお休みです</t>
-  </si>
-  <si>
     <t>那覇市
 (B001)</t>
   </si>
@@ -1936,29 +1926,8 @@
 電話：098-941-7808</t>
   </si>
   <si>
-    <t>9:00～18:30
-ただし年末年始(12/31〜1/2)はお休みです</t>
-  </si>
-  <si>
     <t>宜野湾市
 (A001)</t>
-  </si>
-  <si>
-    <t>【火曜日以外】宜野湾市立博物館
-沖縄県宜野湾市真志喜1-25-1
-電話：098-870-9317
-【火曜日】宜野湾市上下水道局業務サービス課
-沖縄県宜野湾市字野嵩730
-電話：098-892-5733
-(問合せ先)
-宜野湾市上下水道局（平日のみ）
-098-892-5733</t>
-  </si>
-  <si>
-    <t>【火曜日以外】9:00～17:00
-火曜日、年末年始・祝日、その他に臨時休館日はお休みです
-【火曜日】9:00～17:00
-年末年始・祝日はお休みです</t>
   </si>
   <si>
     <t>宜野湾市
@@ -1974,12 +1943,6 @@
 （問合せ先）
 宜野湾市上下水道局業務サービス課排水設備係
 電話:098-892-5733</t>
-  </si>
-  <si>
-    <t>【火曜日以外】9：00～17：00
-ただし、年末年始はお休みです
-【火曜日】9：00～17：00
-ただし、祝日及び年末年始はお休みです</t>
   </si>
   <si>
     <t>名護市
@@ -2008,11 +1971,6 @@
 電話:0980-53-1212(内355)</t>
   </si>
   <si>
-    <t>【平日】9:00～17:00
-【土日・祝日】10:00～17:00
-ただし、1/1～1/3はお休みです</t>
-  </si>
-  <si>
     <t>名護市
 (C001)</t>
   </si>
@@ -2025,11 +1983,6 @@
 電話:0980-53-1212（内355）</t>
   </si>
   <si>
-    <t>【平日】9：00～17：00
-【土日祝日】10：00～17：00
-ただし、1/1～1/3はお休みです</t>
-  </si>
-  <si>
     <t>こちらからご確認ください
 ※現在、在庫数が少ないため、カードが無くなった場合は配布を一時中止します。新たに納入した場合は、名護市のＨＰにてお知らせします</t>
   </si>
@@ -2042,22 +1995,12 @@
 電話:098-989-5066</t>
   </si>
   <si>
-    <t>エイサー会館の営業時間内に配布します。
-開館時間：10:00
-終了時間：時期により異なりますので、エイサー会館HP、またはお電話にてご確認ください。
-ただし、水曜日（休日の場合は翌平日）と年末年始(12/31-1/1）はお休みです</t>
-  </si>
-  <si>
     <t>うるま市</t>
   </si>
   <si>
     <t>うるま市観光案内所（あまわりパーク観光ターミナル）
 沖縄県うるま市勝連南風原3807-2
 電話：098-978-7373</t>
-  </si>
-  <si>
-    <t>9:00～17:30　
-ただし、臨時休館日はお休みです</t>
   </si>
   <si>
     <t>宮古島市
@@ -2072,11 +2015,6 @@
 電話:0980-72-2235</t>
   </si>
   <si>
-    <t>【平日】9:00～17:00
-【土日】10:00～17:30			
-ただし、祝日、閉館日、年末年始はお休みです</t>
-  </si>
-  <si>
     <t>本部町</t>
   </si>
   <si>
@@ -2086,10 +2024,6 @@
 （問合せ先）
 本部町役場上下水道課
 電話:0980-47-5515</t>
-  </si>
-  <si>
-    <t>9:00～18:00
-ただし、12月31日は15:00まで、1月1,2,3日は休みです</t>
   </si>
   <si>
     <t>宜野座村</t>
@@ -2104,23 +2038,135 @@
 電話：098-968-5136</t>
   </si>
   <si>
+    <t>北谷町
+(A001)</t>
+  </si>
+  <si>
+    <t>北谷町観光情報センター沖縄県中頭郡北谷町字美浜16-3電話：098-926-5678
+（問い合わせ先）北谷町上下水道部 上下水道課電話：098-982-7713</t>
+  </si>
+  <si>
+    <t>北谷町
+(B001)</t>
+  </si>
+  <si>
+    <t>中城村</t>
+  </si>
+  <si>
+    <t>中城城跡共同管理協議会沖縄県中頭郡北中城村字大城503電話：098-935-5719</t>
+  </si>
+  <si>
+    <t>沖縄観光情報センター
+沖縄県那覇市泉﨑1-20ｰ6カフーナ旭橋A街区2階
+電話：098ｰ953ｰ8271
+（問い合わせ先）
+沖縄県土木建築部 下水道課
+電話：098-866-2248</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>8:00～19:30（4～6月､10月､11月）　
+8:00～20:30（7～9月）
+8:00～18:30（12～3月）
+（7月の第1水曜日とその翌日は休み）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>9：00～20：00
+ただし1月1日はお休みです</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>9:00～18:30
+ただし年末年始(12/31〜1/2)はお休みです</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>9：00～17：00（年中無休）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【火曜日以外】9:00～17:00
+火曜日、年末年始・祝日、その他に臨時休館日はお休みです
+【火曜日】9:00～17:00
+年末年始・祝日はお休みです</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【火曜日以外】宜野湾市立博物館
+沖縄県宜野湾市真志喜1-25-1
+電話：098-870-9317
+【火曜日】宜野湾市上下水道局業務サービス課
+沖縄県宜野湾市字野嵩730
+電話：098-892-5733
+(問合せ先)
+宜野湾市上下水道局（平日のみ）
+098-892-5733</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【火曜日以外】9：00～17：00
+ただし、年末年始はお休みです
+【火曜日】9：00～17：00
+ただし、祝日及び年末年始はお休みです</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【平日】9:00～17:00
+【土日・祝日】10:00～17:00
+ただし、1/1～1/3はお休みです</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【平日】9：00～17：00
+【土日祝日】10：00～17：00
+ただし、1/1～1/3はお休みです</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>エイサー会館の営業時間内に配布します。
+開館時間：10:00
+終了時間：時期により異なりますので、エイサー会館HP、またはお電話にてご確認ください。
+ただし、水曜日（休日の場合は翌平日）と年末年始(12/31-1/1）はお休みです</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>9:00～17:30　
+ただし、臨時休館日はお休みです</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【平日】9:00～17:00
+【土日】10:00～17:30			
+ただし、祝日、閉館日、年末年始はお休みです</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>9:00～18:00
+ただし、12月31日は15:00まで、1月1,2,3日は休みです</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
     <t>9：15～17：30
 ただし、施設メンテナンスや台風時は臨時休館します</t>
-  </si>
-  <si>
-    <t>北谷町
-(A001)</t>
-  </si>
-  <si>
-    <t>北谷町観光情報センター沖縄県中頭郡北谷町字美浜16-3電話：098-926-5678
-（問い合わせ先）北谷町上下水道部 上下水道課電話：098-982-7713</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>9:00～18:00ただし、年末年始（12/29～1/3）はお休みです</t>
-  </si>
-  <si>
-    <t>北谷町
-(B001)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【平日】8:30～17:15 （12:00～13:00を除く）
+【土日】9:00～17:00
+※博物館の臨時休館日についてはHPをご確認ください
+※年末年始（12/29～1/3）はお休みです
+【祝日】9:00～18:00
+ただし、年末年始（12/29～1/3）はお休みです</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>【10～4月】8：30～17：00【5～9月】8：30～18：00</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>【平日】北谷町上下水道庁舎内下水道係カウンター
@@ -2135,31 +2181,6 @@
 (問合せ先)
 北谷町上下水道部上下水道課
 電話：098-982-7713</t>
-  </si>
-  <si>
-    <t>【平日】8:30～17:15 （12:00～13:00を除く）
-【土日】9:00～17:00
-※博物館の臨時休館日についてはHPをご確認ください
-※年末年始（12/29～1/3）はお休みです
-【祝日】9:00～18:00
-ただし、年末年始（12/29～1/3）はお休みです</t>
-  </si>
-  <si>
-    <t>中城村</t>
-  </si>
-  <si>
-    <t>中城城跡共同管理協議会沖縄県中頭郡北中城村字大城503電話：098-935-5719</t>
-  </si>
-  <si>
-    <t>【10～4月】8：30～17：00【5～9月】8：30～18：00</t>
-  </si>
-  <si>
-    <t>沖縄観光情報センター
-沖縄県那覇市泉﨑1-20ｰ6カフーナ旭橋A街区2階
-電話：098ｰ953ｰ8271
-（問い合わせ先）
-沖縄県土木建築部 下水道課
-電話：098-866-2248</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2206,7 +2227,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2214,12 +2235,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2382,12 +2397,12 @@
     </filterColumn>
   </autoFilter>
   <tableColumns count="6">
-    <tableColumn id="2" xr3:uid="{25703A55-CF45-4E6E-AA21-1F39B22E9A08}" uniqueName="2" name="市町村" queryTableFieldId="2" dataDxfId="17"/>
-    <tableColumn id="4" xr3:uid="{F259FC2F-21FE-4D77-9BFD-E7E1D25A3CEF}" uniqueName="4" name="弾数" queryTableFieldId="4" dataDxfId="16"/>
-    <tableColumn id="5" xr3:uid="{D56F8CD7-17D9-4993-A56D-C88B45CE4383}" uniqueName="5" name="発行年月日" queryTableFieldId="5" dataDxfId="15"/>
-    <tableColumn id="6" xr3:uid="{DCB0CF24-B483-4FCF-87D3-0BD6B8AC1F1D}" uniqueName="6" name="配布場所" queryTableFieldId="6" dataDxfId="14"/>
-    <tableColumn id="7" xr3:uid="{0669D0C1-CF73-4B15-AC0C-4F790C05D29A}" uniqueName="7" name="配布時間" queryTableFieldId="7" dataDxfId="13"/>
-    <tableColumn id="8" xr3:uid="{729A8044-3D52-4174-B30A-2FC226000D05}" uniqueName="8" name="在庫状況" queryTableFieldId="8" dataDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{25703A55-CF45-4E6E-AA21-1F39B22E9A08}" uniqueName="2" name="市町村" queryTableFieldId="2" dataDxfId="5"/>
+    <tableColumn id="4" xr3:uid="{F259FC2F-21FE-4D77-9BFD-E7E1D25A3CEF}" uniqueName="4" name="弾数" queryTableFieldId="4" dataDxfId="4"/>
+    <tableColumn id="5" xr3:uid="{D56F8CD7-17D9-4993-A56D-C88B45CE4383}" uniqueName="5" name="発行年月日" queryTableFieldId="5" dataDxfId="3"/>
+    <tableColumn id="6" xr3:uid="{DCB0CF24-B483-4FCF-87D3-0BD6B8AC1F1D}" uniqueName="6" name="配布場所" queryTableFieldId="6" dataDxfId="2"/>
+    <tableColumn id="7" xr3:uid="{0669D0C1-CF73-4B15-AC0C-4F790C05D29A}" uniqueName="7" name="配布時間" queryTableFieldId="7" dataDxfId="1"/>
+    <tableColumn id="8" xr3:uid="{729A8044-3D52-4174-B30A-2FC226000D05}" uniqueName="8" name="在庫状況" queryTableFieldId="8" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2395,20 +2410,14 @@
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{56B918A5-5858-4144-85CD-07EE4C281E52}" name="沖縄県のマンホールカード" displayName="沖縄県のマンホールカード" ref="A1:F18" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:F18" xr:uid="{56B918A5-5858-4144-85CD-07EE4C281E52}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="第02弾"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:F18" xr:uid="{56B918A5-5858-4144-85CD-07EE4C281E52}"/>
   <tableColumns count="6">
-    <tableColumn id="2" xr3:uid="{394F5FF8-6317-49C2-8EC3-8511CB232061}" uniqueName="2" name="市町村" queryTableFieldId="2" dataDxfId="5"/>
-    <tableColumn id="4" xr3:uid="{E8552616-FC03-4855-BBA2-6F8F4003408E}" uniqueName="4" name="弾数" queryTableFieldId="4" dataDxfId="4"/>
-    <tableColumn id="5" xr3:uid="{A0F28FBF-2FE2-44C9-A4B6-1398AFFE15CF}" uniqueName="5" name="発行年月日" queryTableFieldId="5" dataDxfId="3"/>
-    <tableColumn id="6" xr3:uid="{73CA3192-BE4D-403A-A81A-631D0AEC36B1}" uniqueName="6" name="配布場所" queryTableFieldId="6" dataDxfId="2"/>
-    <tableColumn id="7" xr3:uid="{D147F511-59EC-4315-BAF4-BB6CFC890CAA}" uniqueName="7" name="配布時間" queryTableFieldId="7" dataDxfId="1"/>
-    <tableColumn id="8" xr3:uid="{4EFB2891-0CB2-48F7-9480-209478D3A80E}" uniqueName="8" name="在庫状況" queryTableFieldId="8" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{394F5FF8-6317-49C2-8EC3-8511CB232061}" uniqueName="2" name="市町村" queryTableFieldId="2" dataDxfId="17"/>
+    <tableColumn id="4" xr3:uid="{E8552616-FC03-4855-BBA2-6F8F4003408E}" uniqueName="4" name="弾数" queryTableFieldId="4" dataDxfId="16"/>
+    <tableColumn id="5" xr3:uid="{A0F28FBF-2FE2-44C9-A4B6-1398AFFE15CF}" uniqueName="5" name="発行年月日" queryTableFieldId="5" dataDxfId="15"/>
+    <tableColumn id="6" xr3:uid="{73CA3192-BE4D-403A-A81A-631D0AEC36B1}" uniqueName="6" name="配布場所" queryTableFieldId="6" dataDxfId="14"/>
+    <tableColumn id="7" xr3:uid="{D147F511-59EC-4315-BAF4-BB6CFC890CAA}" uniqueName="7" name="配布時間" queryTableFieldId="7" dataDxfId="13"/>
+    <tableColumn id="8" xr3:uid="{4EFB2891-0CB2-48F7-9480-209478D3A80E}" uniqueName="8" name="在庫状況" queryTableFieldId="8" dataDxfId="12"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5264,342 +5273,342 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="144" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="3" t="s">
+      <c r="A2" t="s">
         <v>405</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" t="s">
         <v>135</v>
       </c>
       <c r="C2" s="1">
         <v>42583</v>
       </c>
-      <c r="D2" s="4" t="s">
-        <v>454</v>
-      </c>
-      <c r="E2" s="3" t="s">
+      <c r="D2" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="E2" t="s">
         <v>240</v>
       </c>
-      <c r="F2" s="3" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="3" t="s">
+      <c r="F2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="108" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" t="s">
         <v>406</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" t="s">
         <v>175</v>
       </c>
       <c r="C3" s="1">
         <v>44576</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" t="s">
         <v>407</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="F3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="54" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" t="s">
         <v>408</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="3" t="s">
-        <v>409</v>
-      </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" t="s">
         <v>82</v>
       </c>
       <c r="C4" s="1">
         <v>43323</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" t="s">
+        <v>409</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="F4" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="54" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" t="s">
         <v>410</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>411</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="3" t="s">
-        <v>412</v>
-      </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" t="s">
         <v>130</v>
       </c>
       <c r="C5" s="1">
         <v>44182</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>413</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>414</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="3" t="s">
-        <v>415</v>
-      </c>
-      <c r="B6" s="3" t="s">
+      <c r="D5" t="s">
+        <v>411</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="F5" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="180" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" t="s">
+        <v>412</v>
+      </c>
+      <c r="B6" t="s">
         <v>15</v>
       </c>
       <c r="C6" s="1">
         <v>44954</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>416</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>417</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="3" t="s">
-        <v>418</v>
-      </c>
-      <c r="B7" s="3" t="s">
+      <c r="D6" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="F6" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="144" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" t="s">
+        <v>413</v>
+      </c>
+      <c r="B7" t="s">
         <v>151</v>
       </c>
       <c r="C7" s="1">
         <v>45275</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>419</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>420</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="3" t="s">
-        <v>421</v>
-      </c>
-      <c r="B8" s="3" t="s">
+      <c r="D7" t="s">
+        <v>414</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="F7" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" t="s">
+        <v>415</v>
+      </c>
+      <c r="B8" t="s">
         <v>119</v>
       </c>
       <c r="C8" s="1">
         <v>43078</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>422</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="3" t="s">
-        <v>423</v>
-      </c>
-      <c r="B9" s="3" t="s">
+      <c r="D8" t="s">
+        <v>416</v>
+      </c>
+      <c r="E8" t="s">
+        <v>441</v>
+      </c>
+      <c r="F8" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="90" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" t="s">
+        <v>417</v>
+      </c>
+      <c r="B9" t="s">
         <v>69</v>
       </c>
       <c r="C9" s="1">
         <v>43946</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>424</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>425</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="3" t="s">
-        <v>426</v>
-      </c>
-      <c r="B10" s="3" t="s">
+      <c r="D9" t="s">
+        <v>418</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="F9" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="90" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" t="s">
+        <v>419</v>
+      </c>
+      <c r="B10" t="s">
         <v>130</v>
       </c>
       <c r="C10" s="1">
         <v>44182</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>427</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>428</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="3" t="s">
-        <v>430</v>
-      </c>
-      <c r="B11" s="3" t="s">
+      <c r="D10" t="s">
+        <v>420</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="F10" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="234" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" t="s">
+        <v>422</v>
+      </c>
+      <c r="B11" t="s">
         <v>69</v>
       </c>
       <c r="C11" s="1">
         <v>43946</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>431</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>432</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="3" t="s">
-        <v>433</v>
-      </c>
-      <c r="B12" s="3" t="s">
+      <c r="D11" t="s">
+        <v>423</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="F11" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="54" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" t="s">
+        <v>424</v>
+      </c>
+      <c r="B12" t="s">
         <v>35</v>
       </c>
       <c r="C12" s="1">
         <v>46010</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>434</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>435</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="3" t="s">
-        <v>436</v>
-      </c>
-      <c r="B13" s="3" t="s">
+      <c r="D12" t="s">
+        <v>425</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="F12" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="72" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" t="s">
+        <v>426</v>
+      </c>
+      <c r="B13" t="s">
         <v>3</v>
       </c>
       <c r="C13" s="1">
         <v>46234</v>
       </c>
-      <c r="D13" s="3" t="s">
-        <v>437</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>438</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="3" t="s">
-        <v>439</v>
-      </c>
-      <c r="B14" s="3" t="s">
+      <c r="D13" t="s">
+        <v>427</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="F13" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="72" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" t="s">
+        <v>428</v>
+      </c>
+      <c r="B14" t="s">
         <v>367</v>
       </c>
       <c r="C14" s="1">
         <v>45863</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>440</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>441</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="3" t="s">
-        <v>442</v>
-      </c>
-      <c r="B15" s="3" t="s">
+      <c r="D14" t="s">
+        <v>429</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="F14" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="72" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" t="s">
+        <v>430</v>
+      </c>
+      <c r="B15" t="s">
         <v>15</v>
       </c>
       <c r="C15" s="1">
         <v>44954</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>443</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>444</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="3" t="s">
-        <v>445</v>
-      </c>
-      <c r="B16" s="3" t="s">
+      <c r="D15" t="s">
+        <v>431</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="F15" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" t="s">
+        <v>432</v>
+      </c>
+      <c r="B16" t="s">
         <v>11</v>
       </c>
       <c r="C16" s="1">
         <v>43218</v>
       </c>
-      <c r="D16" s="3" t="s">
-        <v>446</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>447</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="3" t="s">
-        <v>448</v>
-      </c>
-      <c r="B17" s="3" t="s">
+      <c r="D16" t="s">
+        <v>433</v>
+      </c>
+      <c r="E16" t="s">
+        <v>452</v>
+      </c>
+      <c r="F16" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="234" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" t="s">
+        <v>434</v>
+      </c>
+      <c r="B17" t="s">
         <v>175</v>
       </c>
       <c r="C17" s="1">
         <v>44576</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>449</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>450</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="3" t="s">
-        <v>451</v>
-      </c>
-      <c r="B18" s="3" t="s">
+      <c r="D17" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="F17" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" t="s">
+        <v>435</v>
+      </c>
+      <c r="B18" t="s">
         <v>97</v>
       </c>
       <c r="C18" s="1">
         <v>42948</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>452</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>453</v>
-      </c>
-      <c r="F18" s="3" t="s">
+      <c r="D18" t="s">
+        <v>436</v>
+      </c>
+      <c r="E18" t="s">
+        <v>454</v>
+      </c>
+      <c r="F18" t="s">
         <v>0</v>
       </c>
     </row>
